--- a/docs/dossiers/dossier-paris-11e-32edb9dd.xlsx
+++ b/docs/dossiers/dossier-paris-11e-32edb9dd.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 12/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 13/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-11e-32edb9dd.xlsx
+++ b/docs/dossiers/dossier-paris-11e-32edb9dd.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 13/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 14/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-11e-32edb9dd.xlsx
+++ b/docs/dossiers/dossier-paris-11e-32edb9dd.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 14/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 15/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-11e-32edb9dd.xlsx
+++ b/docs/dossiers/dossier-paris-11e-32edb9dd.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 15/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 16/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-11e-32edb9dd.xlsx
+++ b/docs/dossiers/dossier-paris-11e-32edb9dd.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 16/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 17/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-11e-32edb9dd.xlsx
+++ b/docs/dossiers/dossier-paris-11e-32edb9dd.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 17/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 18/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-11e-32edb9dd.xlsx
+++ b/docs/dossiers/dossier-paris-11e-32edb9dd.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 18/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 19/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>
@@ -2309,7 +2309,7 @@
       </c>
       <c r="B12" s="29" t="inlineStr">
         <is>
-          <t>⚠ Information contradictoire entre le titre/la case structurée (murs libres) et le texte de la description (murs occupés) — à vérifier directement avec l'annonceur avant toute offre. Rue Saint Maur, murs de boutique de 26m² vendus occupés. CARACTERISTIQUES DE L'OFFRE Dans un immeuble ancien, bien entretenu : Une boutique occupée de 26m² (carrez) comprenant au RDC : - une surface de vente - une arrrière-boutique - une cave Superficie Carrez : 25,64m² Boutique : 16,21m² / arrière boutique 9,43m² Loyer annuel : 13 959 € Bail en date du : 1 avril 2021. Activité du locataire : Alimentation sans cuisine ou à consommer sur place. Idéal pour investisseur Rentabilité brut actuelle de 6,98 % CONDITIONS FINANCIERES Prix de vente : 200 000€ Net Vendeur Honoraires en sus à la charge de l'acquéreur : 5% HT Disponibilité : Après accord</t>
+          <t>Bercail Immobilier vous propose ce local commercial de 23 m², idéalement situé dans le 11e arrondissement de Paris, dans un quartier vivant et commerçant. Pensé pour un commerce de proximité, concept store ou bureau de consultation, ce rez-de-chaussée offre une belle visibilité sur rue, un agencement optimisé en open space et des sanitaires privatifs. Vous profiterez de la diversité des restaurants, cafés et boutiques du secteur, ainsi que d'un accès rapide aux transports : métro Voltaire (ligne 9) à environ 300 m et Bastille à 750 m, facilitant l'accueil de la clientèle et la desserte pour la livraison. Proche aussi des espaces verts et d'une offre culturelle dynamique, ce local séduit par son emplacement stratégique au cœur d'un arrondissement recherché. Informations financières : taxe foncière 480 € par an. Charges de copropriété : 150 € par trimestre (soit 50 € / mois). Local vendu loué (950 € / mois). Opportunité intéressante pour investisseur recherchant un rendement locatif stable. Atouts : surface optimisable, faible charges, emplacement central et accessibilité. Rareté sur le marché des petites surfaces commerciales parisiennes. Montant estimé des dépenses annuelles d'énergie pour un usage standard : entre 600 € et 1200 € par an. Prix moyens des énergies indexés sur l'année 2021 (abonnements compris).</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-11e-32edb9dd.xlsx
+++ b/docs/dossiers/dossier-paris-11e-32edb9dd.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 19/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 20/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-11e-32edb9dd.xlsx
+++ b/docs/dossiers/dossier-paris-11e-32edb9dd.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 20/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 21/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>
@@ -929,7 +929,7 @@
     <row r="13">
       <c r="A13" s="13" t="inlineStr">
         <is>
-          <t>EN CLAIR — aux hypothèses de ce dossier (apport 20 %, crédit 4,9 % sur 20 ans, charges provisionnées), il reste environ 144 €/mois à financer en plus du loyer — marge de négociation ou apport supplémentaire à prévoir.</t>
+          <t>EN CLAIR — aux hypothèses de ce dossier (apport 20 %, crédit 3,9 % sur 20 ans, charges provisionnées), il reste environ 51 €/mois à financer en plus du loyer — marge de négociation ou apport supplémentaire à prévoir.</t>
         </is>
       </c>
     </row>
@@ -1082,7 +1082,7 @@
         </is>
       </c>
       <c r="B28" s="20" t="n">
-        <v>0.049</v>
+        <v>0.039</v>
       </c>
     </row>
     <row r="29">

--- a/docs/dossiers/dossier-paris-11e-32edb9dd.xlsx
+++ b/docs/dossiers/dossier-paris-11e-32edb9dd.xlsx
@@ -929,7 +929,7 @@
     <row r="13">
       <c r="A13" s="13" t="inlineStr">
         <is>
-          <t>EN CLAIR — aux hypothèses de ce dossier (apport 20 %, crédit 3,9 % sur 20 ans, charges provisionnées), il reste environ 51 €/mois à financer en plus du loyer — marge de négociation ou apport supplémentaire à prévoir.</t>
+          <t>EN CLAIR — aux hypothèses de ce dossier (apport 20 %, crédit 4,9 % sur 20 ans, charges provisionnées), il reste environ 144 €/mois à financer en plus du loyer — marge de négociation ou apport supplémentaire à prévoir.</t>
         </is>
       </c>
     </row>
@@ -1082,7 +1082,7 @@
         </is>
       </c>
       <c r="B28" s="20" t="n">
-        <v>0.039</v>
+        <v>0.049</v>
       </c>
     </row>
     <row r="29">

--- a/docs/dossiers/dossier-paris-11e-32edb9dd.xlsx
+++ b/docs/dossiers/dossier-paris-11e-32edb9dd.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 21/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 22/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-11e-32edb9dd.xlsx
+++ b/docs/dossiers/dossier-paris-11e-32edb9dd.xlsx
@@ -12,7 +12,7 @@
     <sheet name="Annonce" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Synthèse'!$A$1:$C$58</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Synthèse'!$A$1:$C$59</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -793,7 +793,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F57"/>
+  <dimension ref="A1:F58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -860,7 +860,7 @@
         </is>
       </c>
       <c r="B8" s="10">
-        <f>B25</f>
+        <f>B26</f>
         <v/>
       </c>
       <c r="E8" s="6" t="inlineStr">
@@ -869,7 +869,7 @@
         </is>
       </c>
       <c r="F8" s="8">
-        <f>B38-(B43+B44+B45)/12</f>
+        <f>B39-(B44+B45+B46)/12</f>
         <v/>
       </c>
     </row>
@@ -880,7 +880,7 @@
         </is>
       </c>
       <c r="B9" s="10">
-        <f>B36</f>
+        <f>B37</f>
         <v/>
       </c>
       <c r="E9" s="6" t="inlineStr">
@@ -889,7 +889,7 @@
         </is>
       </c>
       <c r="F9" s="8">
-        <f>B49</f>
+        <f>B50</f>
         <v/>
       </c>
     </row>
@@ -900,7 +900,7 @@
         </is>
       </c>
       <c r="B10" s="11">
-        <f>B38</f>
+        <f>B39</f>
         <v/>
       </c>
     </row>
@@ -911,7 +911,7 @@
         </is>
       </c>
       <c r="B11" s="11">
-        <f>B49</f>
+        <f>B50</f>
         <v/>
       </c>
     </row>
@@ -922,14 +922,14 @@
         </is>
       </c>
       <c r="B12" s="12">
-        <f>B54</f>
+        <f>B55</f>
         <v/>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="13" t="inlineStr">
         <is>
-          <t>EN CLAIR — aux hypothèses de ce dossier (apport 20 %, crédit 4,9 % sur 20 ans, charges provisionnées), il reste environ 144 €/mois à financer en plus du loyer — marge de négociation ou apport supplémentaire à prévoir.</t>
+          <t>EN CLAIR — aux hypothèses de ce dossier (apport 20 %, crédit 4,9 % sur 20 ans, charges provisionnées), il reste environ 87 €/mois à financer en plus du loyer — marge de négociation ou apport supplémentaire à prévoir.</t>
         </is>
       </c>
     </row>
@@ -970,7 +970,7 @@
         </is>
       </c>
       <c r="B18" s="17" t="n">
-        <v>200000</v>
+        <v>190000</v>
       </c>
     </row>
     <row r="19">
@@ -1012,7 +1012,7 @@
       </c>
       <c r="C21" s="18" t="inlineStr">
         <is>
-          <t>ce bien est 9 % au-dessus de la médiane locale</t>
+          <t>ce bien est 4 % au-dessus de la médiane locale</t>
         </is>
       </c>
     </row>
@@ -1033,364 +1033,381 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="18" customHeight="1">
-      <c r="A24" s="7" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="14" t="inlineStr">
+        <is>
+          <t>Évolution du prix demandé</t>
+        </is>
+      </c>
+      <c r="B23" s="15" t="inlineStr">
+        <is>
+          <t>200 000 € (06/07) → 190 000 € (23/09)  —  −5.0 % depuis la première vue</t>
+        </is>
+      </c>
+      <c r="C23" s="18" t="inlineStr">
+        <is>
+          <t>un prix qui baisse est un levier de négociation documenté</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="18" customHeight="1">
+      <c r="A25" s="7" t="inlineStr">
         <is>
           <t>HYPOTHÈSES — cellules jaunes à ajuster avec votre conseiller</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="14" t="inlineStr">
-        <is>
-          <t>Prix négocié retenu</t>
-        </is>
-      </c>
-      <c r="B25" s="19" t="n">
-        <v>200000</v>
-      </c>
-      <c r="C25" s="18" t="inlineStr">
-        <is>
-          <t>par défaut le prix affiché — un prix demandé se négocie</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="14" t="inlineStr">
         <is>
-          <t>Frais d'acquisition (notaire, garanties)</t>
-        </is>
-      </c>
-      <c r="B26" s="20" t="n">
-        <v>0.08</v>
+          <t>Prix négocié retenu</t>
+        </is>
+      </c>
+      <c r="B26" s="19" t="n">
+        <v>190000</v>
+      </c>
+      <c r="C26" s="18" t="inlineStr">
+        <is>
+          <t>par défaut le prix affiché — un prix demandé se négocie</t>
+        </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="14" t="inlineStr">
         <is>
-          <t>Apport personnel</t>
+          <t>Frais d'acquisition (notaire, garanties)</t>
         </is>
       </c>
       <c r="B27" s="20" t="n">
-        <v>0.2</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="14" t="inlineStr">
         <is>
-          <t>Taux du crédit (hors assurance)</t>
+          <t>Apport personnel</t>
         </is>
       </c>
       <c r="B28" s="20" t="n">
-        <v>0.049</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="14" t="inlineStr">
         <is>
-          <t>Durée du crédit (années)</t>
-        </is>
-      </c>
-      <c r="B29" s="21" t="n">
-        <v>20</v>
+          <t>Taux du crédit (hors assurance)</t>
+        </is>
+      </c>
+      <c r="B29" s="20" t="n">
+        <v>0.049</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="14" t="inlineStr">
         <is>
-          <t>Taxe foncière (en mois de loyer par an)</t>
-        </is>
-      </c>
-      <c r="B30" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="C30" s="18" t="inlineStr">
-        <is>
-          <t>à remplacer par le montant réel dès que connu</t>
-        </is>
+          <t>Durée du crédit (années)</t>
+        </is>
+      </c>
+      <c r="B30" s="21" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="14" t="inlineStr">
         <is>
-          <t>Provision entretien &amp; vacance (% du loyer)</t>
-        </is>
-      </c>
-      <c r="B31" s="20" t="n">
-        <v>0.05</v>
+          <t>Taxe foncière (en mois de loyer par an)</t>
+        </is>
+      </c>
+      <c r="B31" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="C31" s="18" t="inlineStr">
+        <is>
+          <t>à remplacer par le montant réel dès que connu</t>
+        </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="14" t="inlineStr">
         <is>
+          <t>Provision entretien &amp; vacance (% du loyer)</t>
+        </is>
+      </c>
+      <c r="B32" s="20" t="n">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="14" t="inlineStr">
+        <is>
           <t>Assurance propriétaire (PNO, €/an)</t>
         </is>
       </c>
-      <c r="B32" s="19" t="n">
+      <c r="B33" s="19" t="n">
         <v>300</v>
       </c>
     </row>
-    <row r="34" ht="18" customHeight="1">
-      <c r="A34" s="7" t="inlineStr">
+    <row r="35" ht="18" customHeight="1">
+      <c r="A35" s="7" t="inlineStr">
         <is>
           <t>PLAN DE FINANCEMENT</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="14" t="inlineStr">
-        <is>
-          <t>Coût d'acquisition total</t>
-        </is>
-      </c>
-      <c r="B35" s="17">
-        <f>B25*(1+B26)</f>
-        <v/>
-      </c>
-      <c r="C35" s="18" t="inlineStr">
-        <is>
-          <t>prix négocié + frais d'acquisition</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="14" t="inlineStr">
         <is>
-          <t>Apport personnel</t>
+          <t>Coût d'acquisition total</t>
         </is>
       </c>
       <c r="B36" s="17">
-        <f>B35*B27</f>
-        <v/>
+        <f>B26*(1+B27)</f>
+        <v/>
+      </c>
+      <c r="C36" s="18" t="inlineStr">
+        <is>
+          <t>prix négocié + frais d'acquisition</t>
+        </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="14" t="inlineStr">
         <is>
-          <t>Montant emprunté</t>
+          <t>Apport personnel</t>
         </is>
       </c>
       <c r="B37" s="17">
-        <f>B35-B36</f>
+        <f>B36*B28</f>
         <v/>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="14" t="inlineStr">
         <is>
-          <t>Mensualité du crédit</t>
-        </is>
-      </c>
-      <c r="B38" s="23">
-        <f>IFERROR(-PMT(B28/12,B29*12,B37),0)</f>
+          <t>Montant emprunté</t>
+        </is>
+      </c>
+      <c r="B38" s="17">
+        <f>B36-B37</f>
         <v/>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="14" t="inlineStr">
         <is>
+          <t>Mensualité du crédit</t>
+        </is>
+      </c>
+      <c r="B39" s="23">
+        <f>IFERROR(-PMT(B29/12,B30*12,B38),0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="14" t="inlineStr">
+        <is>
           <t>Service de la dette (annuel)</t>
         </is>
       </c>
-      <c r="B39" s="17">
-        <f>B38*12</f>
-        <v/>
-      </c>
-    </row>
-    <row r="41" ht="18" customHeight="1">
-      <c r="A41" s="7" t="inlineStr">
+      <c r="B40" s="17">
+        <f>B39*12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42" ht="18" customHeight="1">
+      <c r="A42" s="7" t="inlineStr">
         <is>
           <t>EXPLOITATION ANNUELLE</t>
         </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="14" t="inlineStr">
-        <is>
-          <t>Loyers annuels HT</t>
-        </is>
-      </c>
-      <c r="B42" s="17">
-        <f>IFERROR(B20*12,0)</f>
-        <v/>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="14" t="inlineStr">
         <is>
-          <t>− Taxe foncière</t>
+          <t>Loyers annuels HT</t>
         </is>
       </c>
       <c r="B43" s="17">
-        <f>-IFERROR(B20*B30,0)</f>
+        <f>IFERROR(B20*12,0)</f>
         <v/>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="14" t="inlineStr">
         <is>
-          <t>− Entretien &amp; vacance locative</t>
+          <t>− Taxe foncière</t>
         </is>
       </c>
       <c r="B44" s="17">
-        <f>-B42*B31</f>
+        <f>-IFERROR(B20*B31,0)</f>
         <v/>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="14" t="inlineStr">
         <is>
-          <t>− Assurance PNO</t>
+          <t>− Entretien &amp; vacance locative</t>
         </is>
       </c>
       <c r="B45" s="17">
-        <f>-B32</f>
+        <f>-B43*B32</f>
         <v/>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="14" t="inlineStr">
         <is>
-          <t>Revenu net avant crédit</t>
+          <t>− Assurance PNO</t>
         </is>
       </c>
       <c r="B46" s="17">
-        <f>B42+B43+B44+B45</f>
+        <f>-B33</f>
         <v/>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="14" t="inlineStr">
         <is>
-          <t>− Remboursement du crédit</t>
+          <t>Revenu net avant crédit</t>
         </is>
       </c>
       <c r="B47" s="17">
-        <f>-B39</f>
+        <f>B43+B44+B45+B46</f>
         <v/>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="14" t="inlineStr">
         <is>
-          <t>Cash-flow annuel</t>
+          <t>− Remboursement du crédit</t>
         </is>
       </c>
       <c r="B48" s="17">
-        <f>B46-B39</f>
+        <f>-B40</f>
         <v/>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="14" t="inlineStr">
         <is>
+          <t>Cash-flow annuel</t>
+        </is>
+      </c>
+      <c r="B49" s="17">
+        <f>B47-B40</f>
+        <v/>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="14" t="inlineStr">
+        <is>
           <t>Cash-flow mensuel</t>
         </is>
       </c>
-      <c r="B49" s="24">
-        <f>B48/12</f>
-        <v/>
-      </c>
-      <c r="C49" s="18" t="inlineStr">
+      <c r="B50" s="24">
+        <f>B49/12</f>
+        <v/>
+      </c>
+      <c r="C50" s="18" t="inlineStr">
         <is>
           <t>positif : le bien se paie tout seul, loyer ≥ crédit + charges</t>
         </is>
       </c>
     </row>
-    <row r="51" ht="18" customHeight="1">
-      <c r="A51" s="7" t="inlineStr">
+    <row r="52" ht="18" customHeight="1">
+      <c r="A52" s="7" t="inlineStr">
         <is>
           <t>LES RATIOS QUE REGARDE LE BANQUIER</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="14" t="inlineStr">
-        <is>
-          <t>Rendement brut</t>
-        </is>
-      </c>
-      <c r="B52" s="25">
-        <f>IFERROR(B42/B25,"")</f>
-        <v/>
-      </c>
-      <c r="C52" s="18" t="inlineStr">
-        <is>
-          <t>loyer annuel ÷ prix — la base de comparaison des biens</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="14" t="inlineStr">
         <is>
-          <t>Rendement net avant crédit</t>
+          <t>Rendement brut</t>
         </is>
       </c>
       <c r="B53" s="25">
-        <f>IFERROR(B46/B35,"")</f>
+        <f>IFERROR(B43/B26,"")</f>
         <v/>
       </c>
       <c r="C53" s="18" t="inlineStr">
         <is>
-          <t>après taxe foncière, entretien et assurance</t>
+          <t>loyer annuel ÷ prix — la base de comparaison des biens</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="14" t="inlineStr">
         <is>
-          <t>DSCR — couverture de la dette</t>
-        </is>
-      </c>
-      <c r="B54" s="26">
-        <f>IFERROR(B46/B39,"")</f>
+          <t>Rendement net avant crédit</t>
+        </is>
+      </c>
+      <c r="B54" s="25">
+        <f>IFERROR(B47/B36,"")</f>
         <v/>
       </c>
       <c r="C54" s="18" t="inlineStr">
         <is>
-          <t>revenu net ÷ crédit : ≥ 1,20 rassure une banque</t>
+          <t>après taxe foncière, entretien et assurance</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="14" t="inlineStr">
         <is>
-          <t>LTV — part financée par la banque</t>
-        </is>
-      </c>
-      <c r="B55" s="25">
-        <f>IFERROR(B37/B25,"")</f>
+          <t>DSCR — couverture de la dette</t>
+        </is>
+      </c>
+      <c r="B55" s="26">
+        <f>IFERROR(B47/B40,"")</f>
         <v/>
       </c>
       <c r="C55" s="18" t="inlineStr">
         <is>
-          <t>≤ 80 % est la zone de confort bancaire</t>
+          <t>revenu net ÷ crédit : ≥ 1,20 rassure une banque</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="14" t="inlineStr">
         <is>
-          <t>Effort d'épargne mensuel si négatif</t>
-        </is>
-      </c>
-      <c r="B56" s="23">
-        <f>MAX(0,-B48/12)</f>
-        <v/>
+          <t>LTV — part financée par la banque</t>
+        </is>
+      </c>
+      <c r="B56" s="25">
+        <f>IFERROR(B38/B26,"")</f>
+        <v/>
+      </c>
+      <c r="C56" s="18" t="inlineStr">
+        <is>
+          <t>≤ 80 % est la zone de confort bancaire</t>
+        </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="14" t="inlineStr">
         <is>
+          <t>Effort d'épargne mensuel si négatif</t>
+        </is>
+      </c>
+      <c r="B57" s="23">
+        <f>MAX(0,-B49/12)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="14" t="inlineStr">
+        <is>
           <t>Score de l'outil de veille</t>
         </is>
       </c>
-      <c r="B57" s="15" t="inlineStr">
-        <is>
-          <t>71/100</t>
-        </is>
-      </c>
-      <c r="C57" s="18" t="inlineStr">
+      <c r="B58" s="15" t="inlineStr">
+        <is>
+          <t>74/100</t>
+        </is>
+      </c>
+      <c r="C58" s="18" t="inlineStr">
         <is>
           <t>rendement, emplacement, prix vs marché, financement, fiscalité</t>
         </is>
@@ -1399,18 +1416,18 @@
   </sheetData>
   <mergeCells count="11">
     <mergeCell ref="A4:B4"/>
-    <mergeCell ref="A41:C41"/>
+    <mergeCell ref="A25:C25"/>
+    <mergeCell ref="A42:C42"/>
     <mergeCell ref="A1:C1"/>
     <mergeCell ref="A3:C3"/>
     <mergeCell ref="A13:C14"/>
-    <mergeCell ref="A34:C34"/>
+    <mergeCell ref="A35:C35"/>
     <mergeCell ref="A15:C15"/>
     <mergeCell ref="A7:C7"/>
-    <mergeCell ref="A24:C24"/>
     <mergeCell ref="A2:C2"/>
-    <mergeCell ref="A51:C51"/>
+    <mergeCell ref="A52:C52"/>
   </mergeCells>
-  <conditionalFormatting sqref="B48">
+  <conditionalFormatting sqref="B49">
     <cfRule type="cellIs" priority="1" operator="greaterThanOrEqual" dxfId="0">
       <formula>0</formula>
     </cfRule>
@@ -1418,7 +1435,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B49">
+  <conditionalFormatting sqref="B50">
     <cfRule type="cellIs" priority="3" operator="greaterThanOrEqual" dxfId="0">
       <formula>0</formula>
     </cfRule>
@@ -1426,7 +1443,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B54">
+  <conditionalFormatting sqref="B55">
     <cfRule type="cellIs" priority="5" operator="greaterThanOrEqual" dxfId="0">
       <formula>1.2</formula>
     </cfRule>
@@ -1503,7 +1520,7 @@
         </is>
       </c>
       <c r="G1">
-        <f>'Synthèse'!B29</f>
+        <f>'Synthèse'!B30</f>
         <v/>
       </c>
     </row>
@@ -1512,7 +1529,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="8">
-        <f>IF(A2&lt;=$G$1,'Synthèse'!$B$37,"")</f>
+        <f>IF(A2&lt;=$G$1,'Synthèse'!$B$38,"")</f>
         <v/>
       </c>
       <c r="C2" s="8">
@@ -1533,7 +1550,7 @@
         </is>
       </c>
       <c r="G2">
-        <f>'Synthèse'!B28</f>
+        <f>'Synthèse'!B29</f>
         <v/>
       </c>
     </row>
@@ -1558,7 +1575,7 @@
         <v/>
       </c>
       <c r="G3">
-        <f>'Synthèse'!B39</f>
+        <f>'Synthèse'!B40</f>
         <v/>
       </c>
     </row>
@@ -2261,7 +2278,7 @@
       </c>
       <c r="B8" s="29" t="inlineStr">
         <is>
-          <t>stable depuis la première vue</t>
+          <t>200 000 € (06/07) → 190 000 € (23/09)  —  −5.0 % depuis la première vue</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-11e-32edb9dd.xlsx
+++ b/docs/dossiers/dossier-paris-11e-32edb9dd.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 22/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 23/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-11e-32edb9dd.xlsx
+++ b/docs/dossiers/dossier-paris-11e-32edb9dd.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 23/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 24/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-11e-32edb9dd.xlsx
+++ b/docs/dossiers/dossier-paris-11e-32edb9dd.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 24/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 25/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-11e-32edb9dd.xlsx
+++ b/docs/dossiers/dossier-paris-11e-32edb9dd.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 25/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 26/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-11e-32edb9dd.xlsx
+++ b/docs/dossiers/dossier-paris-11e-32edb9dd.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 26/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 27/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-11e-32edb9dd.xlsx
+++ b/docs/dossiers/dossier-paris-11e-32edb9dd.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 27/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 28/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-11e-32edb9dd.xlsx
+++ b/docs/dossiers/dossier-paris-11e-32edb9dd.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 28/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 29/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-11e-32edb9dd.xlsx
+++ b/docs/dossiers/dossier-paris-11e-32edb9dd.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 29/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 30/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-11e-32edb9dd.xlsx
+++ b/docs/dossiers/dossier-paris-11e-32edb9dd.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 30/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 01/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-11e-32edb9dd.xlsx
+++ b/docs/dossiers/dossier-paris-11e-32edb9dd.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 01/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 02/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-11e-32edb9dd.xlsx
+++ b/docs/dossiers/dossier-paris-11e-32edb9dd.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 02/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 03/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>
@@ -929,7 +929,7 @@
     <row r="13">
       <c r="A13" s="13" t="inlineStr">
         <is>
-          <t>EN CLAIR — aux hypothèses de ce dossier (apport 20 %, crédit 4,9 % sur 20 ans, charges provisionnées), il reste environ 87 €/mois à financer en plus du loyer — marge de négociation ou apport supplémentaire à prévoir.</t>
+          <t>EN CLAIR — aux hypothèses de ce dossier (apport 20 %, crédit 4,9 % sur 20 ans, charges provisionnées), il reste environ 144 €/mois à financer en plus du loyer — marge de négociation ou apport supplémentaire à prévoir.</t>
         </is>
       </c>
     </row>
@@ -970,7 +970,7 @@
         </is>
       </c>
       <c r="B18" s="17" t="n">
-        <v>190000</v>
+        <v>200000</v>
       </c>
     </row>
     <row r="19">
@@ -1012,7 +1012,7 @@
       </c>
       <c r="C21" s="18" t="inlineStr">
         <is>
-          <t>ce bien est 4 % au-dessus de la médiane locale</t>
+          <t>ce bien est 9 % au-dessus de la médiane locale</t>
         </is>
       </c>
     </row>
@@ -1041,7 +1041,7 @@
       </c>
       <c r="B23" s="15" t="inlineStr">
         <is>
-          <t>200 000 € (06/07) → 190 000 € (23/09)  —  −5.0 % depuis la première vue</t>
+          <t>200 000 € (06/07) → 190 000 € (23/09) → 200 000 € (03/10)  —  +0.0 % depuis la première vue</t>
         </is>
       </c>
       <c r="C23" s="18" t="inlineStr">
@@ -1064,7 +1064,7 @@
         </is>
       </c>
       <c r="B26" s="19" t="n">
-        <v>190000</v>
+        <v>200000</v>
       </c>
       <c r="C26" s="18" t="inlineStr">
         <is>
@@ -1404,7 +1404,7 @@
       </c>
       <c r="B58" s="15" t="inlineStr">
         <is>
-          <t>74/100</t>
+          <t>71/100</t>
         </is>
       </c>
       <c r="C58" s="18" t="inlineStr">
@@ -2278,7 +2278,7 @@
       </c>
       <c r="B8" s="29" t="inlineStr">
         <is>
-          <t>200 000 € (06/07) → 190 000 € (23/09)  —  −5.0 % depuis la première vue</t>
+          <t>200 000 € (06/07) → 190 000 € (23/09) → 200 000 € (03/10)  —  +0.0 % depuis la première vue</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-11e-32edb9dd.xlsx
+++ b/docs/dossiers/dossier-paris-11e-32edb9dd.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 03/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 04/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-11e-32edb9dd.xlsx
+++ b/docs/dossiers/dossier-paris-11e-32edb9dd.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 04/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 05/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-11e-32edb9dd.xlsx
+++ b/docs/dossiers/dossier-paris-11e-32edb9dd.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 05/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 06/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-11e-32edb9dd.xlsx
+++ b/docs/dossiers/dossier-paris-11e-32edb9dd.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 06/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 07/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-11e-32edb9dd.xlsx
+++ b/docs/dossiers/dossier-paris-11e-32edb9dd.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 07/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 08/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-11e-32edb9dd.xlsx
+++ b/docs/dossiers/dossier-paris-11e-32edb9dd.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 08/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 09/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-11e-32edb9dd.xlsx
+++ b/docs/dossiers/dossier-paris-11e-32edb9dd.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 09/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 10/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-11e-32edb9dd.xlsx
+++ b/docs/dossiers/dossier-paris-11e-32edb9dd.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 10/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 11/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-11e-32edb9dd.xlsx
+++ b/docs/dossiers/dossier-paris-11e-32edb9dd.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 11/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 12/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-11e-32edb9dd.xlsx
+++ b/docs/dossiers/dossier-paris-11e-32edb9dd.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 12/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 13/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>
@@ -929,7 +929,7 @@
     <row r="13">
       <c r="A13" s="13" t="inlineStr">
         <is>
-          <t>EN CLAIR — aux hypothèses de ce dossier (apport 20 %, crédit 4,9 % sur 20 ans, charges provisionnées), il reste environ 144 €/mois à financer en plus du loyer — marge de négociation ou apport supplémentaire à prévoir.</t>
+          <t>EN CLAIR — aux hypothèses de ce dossier (apport 20 %, crédit 5,34 % sur 20 ans, charges provisionnées), il reste environ 186 €/mois à financer en plus du loyer — marge de négociation ou apport supplémentaire à prévoir.</t>
         </is>
       </c>
     </row>
@@ -1099,7 +1099,7 @@
         </is>
       </c>
       <c r="B29" s="20" t="n">
-        <v>0.049</v>
+        <v>0.0534</v>
       </c>
     </row>
     <row r="30">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="B58" s="15" t="inlineStr">
         <is>
-          <t>71/100</t>
+          <t>69/100</t>
         </is>
       </c>
       <c r="C58" s="18" t="inlineStr">

--- a/docs/dossiers/dossier-paris-11e-32edb9dd.xlsx
+++ b/docs/dossiers/dossier-paris-11e-32edb9dd.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 13/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 14/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-11e-32edb9dd.xlsx
+++ b/docs/dossiers/dossier-paris-11e-32edb9dd.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 14/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 15/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-11e-32edb9dd.xlsx
+++ b/docs/dossiers/dossier-paris-11e-32edb9dd.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 15/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 16/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-11e-32edb9dd.xlsx
+++ b/docs/dossiers/dossier-paris-11e-32edb9dd.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 16/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 17/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-11e-32edb9dd.xlsx
+++ b/docs/dossiers/dossier-paris-11e-32edb9dd.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 17/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 18/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-11e-32edb9dd.xlsx
+++ b/docs/dossiers/dossier-paris-11e-32edb9dd.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 18/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 19/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-11e-32edb9dd.xlsx
+++ b/docs/dossiers/dossier-paris-11e-32edb9dd.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 19/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 20/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-11e-32edb9dd.xlsx
+++ b/docs/dossiers/dossier-paris-11e-32edb9dd.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 20/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 21/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-11e-32edb9dd.xlsx
+++ b/docs/dossiers/dossier-paris-11e-32edb9dd.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 21/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 22/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-11e-32edb9dd.xlsx
+++ b/docs/dossiers/dossier-paris-11e-32edb9dd.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 22/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 23/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-11e-32edb9dd.xlsx
+++ b/docs/dossiers/dossier-paris-11e-32edb9dd.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 23/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 24/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-11e-32edb9dd.xlsx
+++ b/docs/dossiers/dossier-paris-11e-32edb9dd.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 24/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 25/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-11e-32edb9dd.xlsx
+++ b/docs/dossiers/dossier-paris-11e-32edb9dd.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 25/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 26/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>
@@ -2314,7 +2314,7 @@
       </c>
       <c r="B11" s="29" t="inlineStr">
         <is>
-          <t>aucune</t>
+          <t>surface_a_ventiler · unite_loyer</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-11e-32edb9dd.xlsx
+++ b/docs/dossiers/dossier-paris-11e-32edb9dd.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 26/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 27/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>
@@ -1404,7 +1404,7 @@
       </c>
       <c r="B58" s="15" t="inlineStr">
         <is>
-          <t>69/100</t>
+          <t>64/100</t>
         </is>
       </c>
       <c r="C58" s="18" t="inlineStr">
@@ -2314,7 +2314,7 @@
       </c>
       <c r="B11" s="29" t="inlineStr">
         <is>
-          <t>surface_a_ventiler · unite_loyer</t>
+          <t>surface_a_ventiler · occupation_contradictoire · occupation_a_confirmer · unite_loyer</t>
         </is>
       </c>
     </row>
@@ -2326,7 +2326,7 @@
       </c>
       <c r="B12" s="29" t="inlineStr">
         <is>
-          <t>Bercail Immobilier vous propose ce local commercial de 23 m², idéalement situé dans le 11e arrondissement de Paris, dans un quartier vivant et commerçant. Pensé pour un commerce de proximité, concept store ou bureau de consultation, ce rez-de-chaussée offre une belle visibilité sur rue, un agencement optimisé en open space et des sanitaires privatifs. Vous profiterez de la diversité des restaurants, cafés et boutiques du secteur, ainsi que d'un accès rapide aux transports : métro Voltaire (ligne 9) à environ 300 m et Bastille à 750 m, facilitant l'accueil de la clientèle et la desserte pour la livraison. Proche aussi des espaces verts et d'une offre culturelle dynamique, ce local séduit par son emplacement stratégique au cœur d'un arrondissement recherché. Informations financières : taxe foncière 480 € par an. Charges de copropriété : 150 € par trimestre (soit 50 € / mois). Local vendu loué (950 € / mois). Opportunité intéressante pour investisseur recherchant un rendement locatif stable. Atouts : surface optimisable, faible charges, emplacement central et accessibilité. Rareté sur le marché des petites surfaces commerciales parisiennes. Montant estimé des dépenses annuelles d'énergie pour un usage standard : entre 600 € et 1200 € par an. Prix moyens des énergies indexés sur l'année 2021 (abonnements compris).</t>
+          <t>⚠ Information contradictoire entre le titre/la case structurée (murs libres) et le texte de la description (murs occupés) — à vérifier directement avec l'annonceur avant toute offre. Rue Saint Maur, murs de boutique de 26m² vendus occupés. CARACTERISTIQUES DE L'OFFRE Dans un immeuble ancien, bien entretenu : Une boutique occupée de 26m² (carrez) comprenant au RDC : - une surface de vente - une arrrière-boutique - une cave Superficie Carrez : 25,64m² Boutique : 16,21m² / arrière boutique 9,43m² Loyer annuel : 13 959 € Bail en date du : 1 avril 2021. Activité du locataire : Alimentation sans cuisine ou à consommer sur place. Idéal pour investisseur Rentabilité brut actuelle de 7,35 % CONDITIONS FINANCIERES Prix de vente : 190 000€ Net Vendeur Honoraires en sus à la charge de l'acquéreur : 5% HT</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-11e-32edb9dd.xlsx
+++ b/docs/dossiers/dossier-paris-11e-32edb9dd.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 27/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 28/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-11e-32edb9dd.xlsx
+++ b/docs/dossiers/dossier-paris-11e-32edb9dd.xlsx
@@ -2314,7 +2314,7 @@
       </c>
       <c r="B11" s="29" t="inlineStr">
         <is>
-          <t>surface_a_ventiler · occupation_contradictoire · occupation_a_confirmer · unite_loyer</t>
+          <t>conflit_prix · surface_a_ventiler · occupation_contradictoire · occupation_a_confirmer</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-11e-32edb9dd.xlsx
+++ b/docs/dossiers/dossier-paris-11e-32edb9dd.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 28/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 29/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-11e-32edb9dd.xlsx
+++ b/docs/dossiers/dossier-paris-11e-32edb9dd.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 29/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 30/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-11e-32edb9dd.xlsx
+++ b/docs/dossiers/dossier-paris-11e-32edb9dd.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 30/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 31/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>
